--- a/src/attributions/attributions_saliency_traj_98.xlsx
+++ b/src/attributions/attributions_saliency_traj_98.xlsx
@@ -2137,1709 +2137,1709 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.02620433084666729</v>
+        <v>0.1487489491701126</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1625630408525467</v>
+        <v>0.5587641596794128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007369479164481163</v>
+        <v>0.1943879276514053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1036650612950325</v>
+        <v>0.03118784725666046</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008833626285195351</v>
+        <v>0.02707447856664658</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1547589004039764</v>
+        <v>0.2186526209115982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02962768822908401</v>
+        <v>0.009592205286026001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0532512441277504</v>
+        <v>0.01738429442048073</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02423838898539543</v>
+        <v>0.1366115212440491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04607455804944038</v>
+        <v>0.04559594392776489</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1366400867700577</v>
+        <v>0.9112516045570374</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008767541497945786</v>
+        <v>0.2480238080024719</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09355147927999496</v>
+        <v>0.1941857933998108</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02044802717864513</v>
+        <v>0.1933421492576599</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1547531485557556</v>
+        <v>0.3226320147514343</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02900668047368526</v>
+        <v>0.2071282565593719</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008361493237316608</v>
+        <v>0.3113859891891479</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02375517413020134</v>
+        <v>0.1550207585096359</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00163926079403609</v>
+        <v>0.1572199165821075</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01491771545261145</v>
+        <v>0.2405309826135635</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009577157907187939</v>
+        <v>0.05602310597896576</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03463337197899818</v>
+        <v>0.2724701464176178</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02896359376609325</v>
+        <v>0.2321222722530365</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009227629750967026</v>
+        <v>0.03888384252786636</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01498647406697273</v>
+        <v>0.09052444994449615</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02756420336663723</v>
+        <v>0.2305095642805099</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02168102748692036</v>
+        <v>0.0456392765045166</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.008543414995074272</v>
+        <v>0.1729840487241745</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.009641565382480621</v>
+        <v>0.0862051248550415</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.009476873092353344</v>
+        <v>0.01509915199130774</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004494990222156048</v>
+        <v>0.1628293544054031</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.007588244043290615</v>
+        <v>0.5129461288452148</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01835079118609428</v>
+        <v>0.2740201354026794</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01115202251821756</v>
+        <v>0.08190114051103592</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.007347557228058577</v>
+        <v>0.1041086837649345</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01587040908634663</v>
+        <v>0.07959569990634918</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0295365396887064</v>
+        <v>0.04799661785364151</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01993954181671143</v>
+        <v>0.187919020652771</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002600298263132572</v>
+        <v>0.01076623424887657</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.005828710272908211</v>
+        <v>0.1661686897277832</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003538534278050065</v>
+        <v>0.03974473103880882</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.02718522027134895</v>
+        <v>0.04839630052447319</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00606278283521533</v>
+        <v>0.1553100049495697</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01533396821469069</v>
+        <v>0.276698499917984</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.01923454366624355</v>
+        <v>0.07714866101741791</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01281832344830036</v>
+        <v>0.09266660362482071</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1166501194238663</v>
+        <v>0.9744449853897095</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.004844744689762592</v>
+        <v>0.1195046454668045</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01697763800621033</v>
+        <v>0.04208792001008987</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.005966796539723873</v>
+        <v>0.1046571135520935</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.08068947494029999</v>
+        <v>0.3807337880134583</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.007660307921469212</v>
+        <v>0.006735524162650108</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0229332447052002</v>
+        <v>0.06637995690107346</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.04030207544565201</v>
+        <v>0.1166214942932129</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.02706237323582172</v>
+        <v>0.05518563091754913</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.04523194581270218</v>
+        <v>0.1455427706241608</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.04671084508299828</v>
+        <v>0.1109217777848244</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02459359169006348</v>
+        <v>0.02750670164823532</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.02345607057213783</v>
+        <v>0.2971364855766296</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.05469697713851929</v>
+        <v>0.03987082466483116</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005182401742786169</v>
+        <v>0.1847235560417175</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.02455797791481018</v>
+        <v>0.02633409202098846</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.006882552988827229</v>
+        <v>0.06006253883242607</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.006606573704630136</v>
+        <v>0.1495187729597092</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05544756725430489</v>
+        <v>0.0990765392780304</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.009289640001952648</v>
+        <v>0.01200393028557301</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.02143483236432076</v>
+        <v>0.1367583423852921</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02123954519629478</v>
+        <v>0.07222191989421844</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.005237782839685678</v>
+        <v>0.1179295033216476</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.02044288069009781</v>
+        <v>0.08425995707511902</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01325099170207977</v>
+        <v>0.05394186824560165</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0001926752738654613</v>
+        <v>0.05118761211633682</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006009210366755724</v>
+        <v>0.2049607783555984</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.06299879401922226</v>
+        <v>0.6286604404449463</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01486259885132313</v>
+        <v>0.02484659105539322</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.02718273364007473</v>
+        <v>0.3105990886688232</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003062496427446604</v>
+        <v>0.1279072910547256</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0365273617208004</v>
+        <v>0.1810374706983566</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.009921745397150517</v>
+        <v>0.05168889462947845</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.005223043262958527</v>
+        <v>0.1436374336481094</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.02541003562510014</v>
+        <v>0.05172249302268028</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001915775123052299</v>
+        <v>0.06092880666255951</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.02086746506392956</v>
+        <v>0.1901889741420746</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.02048926800489426</v>
+        <v>0.02138692513108253</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0185958705842495</v>
+        <v>0.04012051224708557</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01041124761104584</v>
+        <v>0.05690474808216095</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02060766145586967</v>
+        <v>0.1022080928087234</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01282194256782532</v>
+        <v>0.1029634177684784</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0125113083049655</v>
+        <v>0.0300239622592926</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.01246373914182186</v>
+        <v>0.04451680928468704</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.02959324233233929</v>
+        <v>0.1380067467689514</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02656352892518044</v>
+        <v>0.6248594522476196</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.005361232440918684</v>
+        <v>0.05963125452399254</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.01780389994382858</v>
+        <v>0.2645373344421387</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003408873453736305</v>
+        <v>0.3855265974998474</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0004484066739678383</v>
+        <v>0.2537412345409393</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0146835669875145</v>
+        <v>0.09278576821088791</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01843849383294582</v>
+        <v>0.04657154530286789</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.003210222814232111</v>
+        <v>0.1849662214517593</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0006099896272644401</v>
+        <v>0.02974545955657959</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.017901960760355</v>
+        <v>0.1750135123729706</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.01836326532065868</v>
+        <v>0.02991762012243271</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02619011327624321</v>
+        <v>0.04134932905435562</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.009293004870414734</v>
+        <v>0.01782545819878578</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02166216820478439</v>
+        <v>0.1002263575792313</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01498304214328527</v>
+        <v>0.05839711427688599</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.02289460599422455</v>
+        <v>0.006038757041096687</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.004938103258609772</v>
+        <v>0.06857755780220032</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001138526480644941</v>
+        <v>0.1215205788612366</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01522280462086201</v>
+        <v>0.08945892751216888</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.008833379484713078</v>
+        <v>0.02945325151085854</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1036456003785133</v>
+        <v>0.1282565742731094</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0112052820622921</v>
+        <v>0.2879583537578583</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.008087888360023499</v>
+        <v>0.09416911005973816</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.01191198453307152</v>
+        <v>0.1726158559322357</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.02825925126671791</v>
+        <v>0.1005919799208641</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.02165839448571205</v>
+        <v>0.01188173145055771</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.01022202242165804</v>
+        <v>0.07926556468009949</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.008316334336996078</v>
+        <v>0.153019517660141</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.01748614758253098</v>
+        <v>0.002221133559942245</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.003844284452497959</v>
+        <v>0.1839397698640823</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.003949547652155161</v>
+        <v>0.1426757425069809</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001878701848909259</v>
+        <v>0.01684596203267574</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.01811949163675308</v>
+        <v>0.1188052594661713</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.000539424829185009</v>
+        <v>0.2577335238456726</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.02121624350547791</v>
+        <v>0.02129921689629555</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0015070466324687</v>
+        <v>0.1609572619199753</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001945187454111874</v>
+        <v>0.03321687132120132</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.01714527048170567</v>
+        <v>0.08000081777572632</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.01122249849140644</v>
+        <v>0.003106851130723953</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.005997250322252512</v>
+        <v>0.1640048921108246</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01347461622208357</v>
+        <v>0.2050632238388062</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.007489819079637527</v>
+        <v>0.08723254501819611</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00228352565318346</v>
+        <v>0.02924228832125664</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.004034289158880711</v>
+        <v>0.01702394708991051</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.009706985205411911</v>
+        <v>0.03639493137598038</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01220774184912443</v>
+        <v>0.02283201925456524</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.01462601218372583</v>
+        <v>0.02021332085132599</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.01018572133034468</v>
+        <v>0.1223573833703995</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0004217363893985748</v>
+        <v>0.07714848220348358</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.02442609705030918</v>
+        <v>0.01693066582083702</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.008634529076516628</v>
+        <v>0.09594554454088211</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.003221737453714013</v>
+        <v>0.09610641747713089</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.003955864813178778</v>
+        <v>0.03679804876446724</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.007922972552478313</v>
+        <v>0.01844510436058044</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004777438007295132</v>
+        <v>0.0416826568543911</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01626287028193474</v>
+        <v>0.0303486417979002</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.01895583607256413</v>
+        <v>0.1116146966814995</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.001181291649118066</v>
+        <v>0.05967885628342628</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.00683626951649785</v>
+        <v>0.006280831061303616</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0226419921964407</v>
+        <v>0.07389730960130692</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.05918643996119499</v>
+        <v>0.104189395904541</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.01111357472836971</v>
+        <v>0.07093915343284607</v>
       </c>
       <c r="EX4" t="n">
-        <v>6.221083458513021e-05</v>
+        <v>0.07082794606685638</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.01559021882712841</v>
+        <v>0.1987692713737488</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.01520712859928608</v>
+        <v>0.01955764554440975</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0204820167273283</v>
+        <v>0.03795778751373291</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.005692728329449892</v>
+        <v>0.01420368812978268</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0178968571126461</v>
+        <v>0.1134137138724327</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.021457364782691</v>
+        <v>0.1445287764072418</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.01495361141860485</v>
+        <v>0.02073418907821178</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.01205797307193279</v>
+        <v>0.05960773676633835</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.006032861769199371</v>
+        <v>0.1058711633086205</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01563992910087109</v>
+        <v>0.2249119877815247</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.01319282501935959</v>
+        <v>0.05992552638053894</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.01930096000432968</v>
+        <v>0.2128706574440002</v>
       </c>
       <c r="FK4" t="n">
-        <v>6.790034240111709e-05</v>
+        <v>0.199320062994957</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.02321168035268784</v>
+        <v>0.02890277467668056</v>
       </c>
       <c r="FM4" t="n">
-        <v>9.811297059059143e-05</v>
+        <v>0.2041301131248474</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01990045979619026</v>
+        <v>0.2204051464796066</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.007701684255152941</v>
+        <v>0.1725239753723145</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0135606937110424</v>
+        <v>0.008711569011211395</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.005173347890377045</v>
+        <v>0.2780651152133942</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.01955744996666908</v>
+        <v>0.08064235746860504</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.03521304205060005</v>
+        <v>0.2249191999435425</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.001622440759092569</v>
+        <v>0.002504767850041389</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01636040024459362</v>
+        <v>0.007184375077486038</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.01889514923095703</v>
+        <v>0.1845589578151703</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.001115520019084215</v>
+        <v>0.01819095760583878</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.00712584936991334</v>
+        <v>0.157189279794693</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.03277172148227692</v>
+        <v>0.1401199400424957</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.00221226061694324</v>
+        <v>0.07162056863307953</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.006149365566670895</v>
+        <v>0.01245357654988766</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.005887632723897696</v>
+        <v>0.1287062615156174</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.01041922625154257</v>
+        <v>0.07738000154495239</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.02629020251333714</v>
+        <v>0.04567780718207359</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.07808005064725876</v>
+        <v>0.1188828945159912</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.004865140188485384</v>
+        <v>0.1429913341999054</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.01678404957056046</v>
+        <v>0.2106338888406754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0004390071844682097</v>
+        <v>0.02114612609148026</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1668816059827805</v>
+        <v>0.5726921558380127</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02141944319009781</v>
+        <v>0.001097425818443298</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1192015931010246</v>
+        <v>0.4184753000736237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07956826686859131</v>
+        <v>0.2269171178340912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07096609473228455</v>
+        <v>0.02279546484351158</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01381024345755577</v>
+        <v>0.01367473229765892</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04139907285571098</v>
+        <v>0.2019202262163162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01509724371135235</v>
+        <v>0.06689797341823578</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005401910282671452</v>
+        <v>0.04163185879588127</v>
       </c>
       <c r="K5" t="n">
-        <v>0.134874701499939</v>
+        <v>0.5735790729522705</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01403117459267378</v>
+        <v>0.01729553937911987</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1147332787513733</v>
+        <v>0.528247594833374</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09553638100624084</v>
+        <v>0.4998641610145569</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07981357723474503</v>
+        <v>0.03388208523392677</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01882201060652733</v>
+        <v>0.06301875412464142</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01125381886959076</v>
+        <v>0.07835490256547928</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03210334852337837</v>
+        <v>0.09059035778045654</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004852649755775928</v>
+        <v>0.002767532598227262</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02168729528784752</v>
+        <v>0.02463990449905396</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01802690699696541</v>
+        <v>0.004856160841882229</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03795328363776207</v>
+        <v>0.07853109389543533</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04291402921080589</v>
+        <v>0.002917000092566013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02019067294895649</v>
+        <v>0.06303561478853226</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0009157417807728052</v>
+        <v>0.01697833091020584</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01297765038907528</v>
+        <v>0.0597633421421051</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01298646070063114</v>
+        <v>0.07490025460720062</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001959564164280891</v>
+        <v>0.02246903069317341</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01908646337687969</v>
+        <v>0.02969259023666382</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005438222549855709</v>
+        <v>0.07461709529161453</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01077514234930277</v>
+        <v>0.2006286829710007</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.03721179068088531</v>
+        <v>0.2039584517478943</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01990124955773354</v>
+        <v>0.2065580189228058</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.008414683863520622</v>
+        <v>0.05771640688180923</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.01160756312310696</v>
+        <v>0.1894417107105255</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02004199288785458</v>
+        <v>0.01045447401702404</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001219010562635958</v>
+        <v>0.01730711385607719</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02130866795778275</v>
+        <v>0.1460694968700409</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.001260299701243639</v>
+        <v>0.06616093963384628</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.01600166410207748</v>
+        <v>0.002971913665533066</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000658039003610611</v>
+        <v>0.1223925352096558</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.02353043481707573</v>
+        <v>0.08479971438646317</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001387106254696846</v>
+        <v>0.1355126202106476</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.01797004789113998</v>
+        <v>0.03263052552938461</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.008191290311515331</v>
+        <v>0.01577172428369522</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.01483499724417925</v>
+        <v>0.06326793879270554</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.07562947273254395</v>
+        <v>0.2919529974460602</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.01815722696483135</v>
+        <v>0.03683583438396454</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03098126128315926</v>
+        <v>0.07967416942119598</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0468234047293663</v>
+        <v>0.2118529677391052</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.02907797694206238</v>
+        <v>0.02643380686640739</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01545749604701996</v>
+        <v>0.2059536725282669</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.02105859108269215</v>
+        <v>0.1214729771018028</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0112916324287653</v>
+        <v>0.002979147247970104</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.007793604861944914</v>
+        <v>0.1027741953730583</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05006313323974609</v>
+        <v>0.0375472865998745</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01280665956437588</v>
+        <v>0.1215678527951241</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.06037153676152229</v>
+        <v>0.1457463502883911</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.09489315003156662</v>
+        <v>0.116488553583622</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.04412947222590446</v>
+        <v>0.06566685438156128</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.006275014020502567</v>
+        <v>0.10672477632761</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.006706149782985449</v>
+        <v>0.1583603769540787</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.009970603510737419</v>
+        <v>0.01387515012174845</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.008619766682386398</v>
+        <v>0.01016796566545963</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.009285056032240391</v>
+        <v>0.04987055063247681</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.00686959270387888</v>
+        <v>0.06478088349103928</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.02188623324036598</v>
+        <v>0.06107450649142265</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0001910814899019897</v>
+        <v>0.03631222620606422</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.008188752457499504</v>
+        <v>0.02047069184482098</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.02494356967508793</v>
+        <v>0.04449382424354553</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0104797538369894</v>
+        <v>0.1268854886293411</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.01177496369928122</v>
+        <v>0.04757024720311165</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0145825631916523</v>
+        <v>0.007794518023729324</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.05161365494132042</v>
+        <v>0.2264473438262939</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.002667550463229418</v>
+        <v>0.05794421955943108</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0199083536863327</v>
+        <v>0.3261404633522034</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.03141935914754868</v>
+        <v>0.07489043474197388</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.00193663639947772</v>
+        <v>0.0293278694152832</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.004298810847103596</v>
+        <v>0.09335663914680481</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.005886521190404892</v>
+        <v>0.002924598520621657</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.02930511720478535</v>
+        <v>0.0163690522313118</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.005339994560927153</v>
+        <v>0.01262523140758276</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.02430110797286034</v>
+        <v>0.2158547639846802</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00173273088876158</v>
+        <v>0.004946524277329445</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02998505719006062</v>
+        <v>0.1246063485741615</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.005715752951800823</v>
+        <v>0.009266605600714684</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.008854684419929981</v>
+        <v>0.04546372219920158</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.008479282259941101</v>
+        <v>0.08459176123142242</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.00309392437338829</v>
+        <v>0.01839460246264935</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0006691025337204337</v>
+        <v>0.02314426377415657</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.001358481356874108</v>
+        <v>0.06937055289745331</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.00110120652243495</v>
+        <v>0.2118014693260193</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001800989964976907</v>
+        <v>0.2944740056991577</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0172771867364645</v>
+        <v>0.348571240901947</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.05740734562277794</v>
+        <v>0.1014057174324989</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.01330643240362406</v>
+        <v>0.2081231027841568</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.03453919664025307</v>
+        <v>0.193669319152832</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.02354790642857552</v>
+        <v>0.0206761509180069</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.00373479095287621</v>
+        <v>0.01582335494458675</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.005152496043592691</v>
+        <v>0.02832159027457237</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.02278447337448597</v>
+        <v>0.2055423855781555</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004371141083538532</v>
+        <v>0.0142470421269536</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02349788881838322</v>
+        <v>0.1464977264404297</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.009850725531578064</v>
+        <v>0.04140099510550499</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02105208672583103</v>
+        <v>0.04456219077110291</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.01061337813735008</v>
+        <v>0.07298378646373749</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0003480447921901941</v>
+        <v>0.01158044952899218</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.006012547761201859</v>
+        <v>0.02102889865636826</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.002243557944893837</v>
+        <v>0.003198259975761175</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.06633327901363373</v>
+        <v>0.02276642620563507</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.02349170297384262</v>
+        <v>0.00429447740316391</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.04135753959417343</v>
+        <v>0.2159399539232254</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01792309060692787</v>
+        <v>0.1325553208589554</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.02212728932499886</v>
+        <v>0.05830282717943192</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.000493926927447319</v>
+        <v>0.2123051583766937</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0009443759918212891</v>
+        <v>0.2418053299188614</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.01537694595754147</v>
+        <v>0.08142803609371185</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.01372290402650833</v>
+        <v>0.0676288977265358</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.02059588022530079</v>
+        <v>0.0934816300868988</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.01547486428171396</v>
+        <v>0.05788495764136314</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.04895665496587753</v>
+        <v>0.1321233958005905</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02494165115058422</v>
+        <v>0.03123786486685276</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0006682410603389144</v>
+        <v>0.02307640388607979</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001724519766867161</v>
+        <v>0.0357927493751049</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.02000041306018829</v>
+        <v>0.1204668134450912</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.01315190270543098</v>
+        <v>0.2731033265590668</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001803454128094018</v>
+        <v>0.04634831845760345</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001271868823096156</v>
+        <v>0.01332116778939962</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.005095706321299076</v>
+        <v>0.06632713973522186</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.001140789361670613</v>
+        <v>0.03162408247590065</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.002320247702300549</v>
+        <v>0.1148616820573807</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.02881537564098835</v>
+        <v>0.1391193121671677</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01290768850594759</v>
+        <v>0.1768417209386826</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0008773221634328365</v>
+        <v>0.2069734334945679</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0009276564233005047</v>
+        <v>0.1885766685009003</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.00016974494792521</v>
+        <v>0.1104830205440521</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00325555307790637</v>
+        <v>0.1451115012168884</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.006168375723063946</v>
+        <v>0.1098127067089081</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001673674676567316</v>
+        <v>0.02802773378789425</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001680875197052956</v>
+        <v>0.1421502083539963</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.00856802798807621</v>
+        <v>0.1041461229324341</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.00214920099824667</v>
+        <v>0.02304631657898426</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.01216037571430206</v>
+        <v>0.04197228327393532</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.008760001510381699</v>
+        <v>0.0253825169056654</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.000426948769018054</v>
+        <v>0.09514924883842468</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0143913496285677</v>
+        <v>0.2178006172180176</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.00330717209726572</v>
+        <v>0.04660802334547043</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.007071460597217083</v>
+        <v>0.1685722172260284</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02307818457484245</v>
+        <v>0.08423913270235062</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.04120669513940811</v>
+        <v>0.04227482154965401</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.01229572109878063</v>
+        <v>0.03974705561995506</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.01404171995818615</v>
+        <v>0.1403608024120331</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.006866054609417915</v>
+        <v>0.001182838343083858</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.005664738826453686</v>
+        <v>0.006045653484761715</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.02482538670301437</v>
+        <v>0.2323021441698074</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001240723417140543</v>
+        <v>0.0008310228586196899</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02619905769824982</v>
+        <v>0.1876918226480484</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.007275337819010019</v>
+        <v>0.03410299867391586</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0180349126458168</v>
+        <v>0.04193674772977829</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0157279297709465</v>
+        <v>0.07981722056865692</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.004761601332575083</v>
+        <v>0.04114043340086937</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001106858951970935</v>
+        <v>9.310571476817131e-05</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0006766760488972068</v>
+        <v>0.01817475445568562</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01845312863588333</v>
+        <v>0.1132885664701462</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.008335902355611324</v>
+        <v>0.04117574915289879</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.01151523739099503</v>
+        <v>0.1420865803956985</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01324106007814407</v>
+        <v>0.02011140249669552</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0231517031788826</v>
+        <v>0.09113481640815735</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004624408669769764</v>
+        <v>0.04404644668102264</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0214653592556715</v>
+        <v>0.04771894216537476</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.006955166347324848</v>
+        <v>0.05458612740039825</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.00914294645190239</v>
+        <v>0.09952642023563385</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.02935934066772461</v>
+        <v>0.3099561631679535</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.01016635727137327</v>
+        <v>0.02176094055175781</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.004924099892377853</v>
+        <v>0.09452858567237854</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.03293886035680771</v>
+        <v>0.256862610578537</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.008288704790174961</v>
+        <v>0.0100058987736702</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05820749327540398</v>
+        <v>0.133448988199234</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.006465547252446413</v>
+        <v>0.2017935216426849</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003792824223637581</v>
+        <v>0.1336269825696945</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0007599950768053532</v>
+        <v>0.02598955482244492</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01385652273893356</v>
+        <v>0.06050232797861099</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.006802438758313656</v>
+        <v>0.0468432679772377</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.01373174879699945</v>
+        <v>0.1410131454467773</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.08395864814519882</v>
+        <v>0.05284326896071434</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.02481918036937714</v>
+        <v>0.03109857812523842</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.05725362524390221</v>
+        <v>0.04662109166383743</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.007945786230266094</v>
+        <v>0.08331212401390076</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01181355956941843</v>
+        <v>0.02033818513154984</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.04966741055250168</v>
+        <v>0.006703290157020092</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1476506739854813</v>
+        <v>0.250282883644104</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04378611966967583</v>
+        <v>0.02372708916664124</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1417827606201172</v>
+        <v>0.239741787314415</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2576279640197754</v>
+        <v>0.01602103933691978</v>
       </c>
       <c r="F6" t="n">
-        <v>0.20000259578228</v>
+        <v>0.06303812563419342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1112138032913208</v>
+        <v>0.04207809269428253</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05671815574169159</v>
+        <v>0.01376385986804962</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1217257231473923</v>
+        <v>0.06004438549280167</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08148683607578278</v>
+        <v>0.02299920469522476</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06563463062047958</v>
+        <v>0.3206673860549927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01298161596059799</v>
+        <v>0.06781837344169617</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1377876698970795</v>
+        <v>0.2750751972198486</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2181730568408966</v>
+        <v>0.02298469096422195</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1034800261259079</v>
+        <v>0.1226272210478783</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04561899602413177</v>
+        <v>0.006291169673204422</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07793068885803223</v>
+        <v>0.0758533775806427</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09435752034187317</v>
+        <v>0.03860189020633698</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01451932638883591</v>
+        <v>0.00502133509144187</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007003224454820156</v>
+        <v>0.04073608666658401</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05124014988541603</v>
+        <v>0.01058841124176979</v>
       </c>
       <c r="V6" t="n">
-        <v>0.108162447810173</v>
+        <v>0.02779215946793556</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1736438721418381</v>
+        <v>0.02499398961663246</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003004615660756826</v>
+        <v>0.02386914938688278</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01995348185300827</v>
+        <v>0.00871460884809494</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03702054917812347</v>
+        <v>0.02591272629797459</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04983071982860565</v>
+        <v>0.06112539023160934</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03679622709751129</v>
+        <v>0.04241156578063965</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07872673869132996</v>
+        <v>0.04637550190091133</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1231985315680504</v>
+        <v>0.02069734595716</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03657511621713638</v>
+        <v>0.02802919782698154</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.056638203561306</v>
+        <v>0.1522244811058044</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02058441936969757</v>
+        <v>0.06486533582210541</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.02944206073880196</v>
+        <v>0.01489920169115067</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06831051409244537</v>
+        <v>0.02021141536533833</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1000531911849976</v>
+        <v>0.01753394305706024</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0240405835211277</v>
+        <v>0.01291673816740513</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03120988421142101</v>
+        <v>0.03756794333457947</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.009889727458357811</v>
+        <v>0.01271749474108219</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07261491566896439</v>
+        <v>0.03570732101798058</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.005904311314225197</v>
+        <v>0.07264874130487442</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.01070646662265062</v>
+        <v>0.02015481144189835</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.04515756294131279</v>
+        <v>0.02859731204807758</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0386628657579422</v>
+        <v>0.04198071360588074</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.03778652101755142</v>
+        <v>0.02854113280773163</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.06044142320752144</v>
+        <v>0.03943199291825294</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.02285652421414852</v>
+        <v>0.03972802683711052</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09258657693862915</v>
+        <v>0.01753523014485836</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.03774760290980339</v>
+        <v>0.1371437013149261</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.213341623544693</v>
+        <v>0.09158162772655487</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1737181842327118</v>
+        <v>0.04780935123562813</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1952494829893112</v>
+        <v>0.003476782701909542</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.03715326637029648</v>
+        <v>0.1146260052919388</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1061955690383911</v>
+        <v>0.09074660390615463</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.02317168563604355</v>
+        <v>0.03890733048319817</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.08089941740036011</v>
+        <v>0.09413157403469086</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01199213042855263</v>
+        <v>0.05178285390138626</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.2685357332229614</v>
+        <v>0.02368311583995819</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.2810813784599304</v>
+        <v>0.005901293829083443</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.03927721083164215</v>
+        <v>0.01422507036477327</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1757026463747025</v>
+        <v>0.009424367919564247</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.008017978630959988</v>
+        <v>0.1206374391913414</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.06057221069931984</v>
+        <v>0.03443878889083862</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.008776217699050903</v>
+        <v>0.01180148869752884</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02517291344702244</v>
+        <v>0.08452747762203217</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.02299828641116619</v>
+        <v>0.01802997477352619</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06165381893515587</v>
+        <v>0.04742527008056641</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0859382376074791</v>
+        <v>0.01686182618141174</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.05204086750745773</v>
+        <v>0.02083838544785976</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1716395914554596</v>
+        <v>0.01477360259741545</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.001751587609760463</v>
+        <v>0.05759645625948906</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0290475245565176</v>
+        <v>0.00632846262305975</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.001710034906864166</v>
+        <v>0.009223021566867828</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001788066467270255</v>
+        <v>0.02647662535309792</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0005586035549640656</v>
+        <v>0.01196683011949062</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.02193097397685051</v>
+        <v>0.0891951397061348</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1913887858390808</v>
+        <v>0.01447959803044796</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.02871143072843552</v>
+        <v>0.0481732115149498</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.120043009519577</v>
+        <v>0.005320747382938862</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.05611307919025421</v>
+        <v>0.04532746225595474</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1075241789221764</v>
+        <v>0.04355127364397049</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.02016713470220566</v>
+        <v>0.003781765233725309</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.01160313189029694</v>
+        <v>0.08664419502019882</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.02105719968676567</v>
+        <v>0.006195084191858768</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.05949924513697624</v>
+        <v>0.06797130405902863</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02454156242311001</v>
+        <v>0.006134139373898506</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.03222160786390305</v>
+        <v>0.02965725027024746</v>
       </c>
       <c r="CJ6" t="n">
-        <v>6.453879177570343e-05</v>
+        <v>0.007914597168564796</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.02239870652556419</v>
+        <v>0.008419713005423546</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.01124594639986753</v>
+        <v>0.00718039134517312</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.05378780514001846</v>
+        <v>0.01690469309687614</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.09085658192634583</v>
+        <v>0.01089799404144287</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.03693127632141113</v>
+        <v>0.06331001967191696</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.227637842297554</v>
+        <v>0.05026964098215103</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.2959787249565125</v>
+        <v>0.1891143918037415</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.08356401324272156</v>
+        <v>0.04812095686793327</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0899084210395813</v>
+        <v>0.01547391805797815</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.09619009494781494</v>
+        <v>0.07943273335695267</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.01664398238062859</v>
+        <v>0.02251508273184299</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.01106912456452847</v>
+        <v>0.0007859077304601669</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02055462077260017</v>
+        <v>0.07886740565299988</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01389832515269518</v>
+        <v>0.001020069932565093</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02702505141496658</v>
+        <v>0.07636456191539764</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.02802114747464657</v>
+        <v>0.006669927388429642</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03799693286418915</v>
+        <v>0.02860773168504238</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.009818460792303085</v>
+        <v>0.004689156077802181</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.004982314072549343</v>
+        <v>0.007373998872935772</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.03787136822938919</v>
+        <v>0.01936992630362511</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01357612758874893</v>
+        <v>0.02940277010202408</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1183664798736572</v>
+        <v>0.08577244728803635</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0188112985342741</v>
+        <v>0.0119280107319355</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.05386701971292496</v>
+        <v>0.06249088793992996</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1013593971729279</v>
+        <v>0.06010181829333305</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.09516658633947372</v>
+        <v>0.009305233135819435</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.03664079308509827</v>
+        <v>0.04298438876867294</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.1083894148468971</v>
+        <v>0.08722265064716339</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0449841246008873</v>
+        <v>0.02485622093081474</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01962243393063545</v>
+        <v>0.002603780478239059</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.07625159621238708</v>
+        <v>0.02630840055644512</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01645456627011299</v>
+        <v>0.02661014534533024</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.212555930018425</v>
+        <v>0.07242581248283386</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.1806102395057678</v>
+        <v>0.04810813069343567</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1771031320095062</v>
+        <v>0.002365035237744451</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.03730294853448868</v>
+        <v>0.02452327683568001</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.06059073656797409</v>
+        <v>0.06820723414421082</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.02613987028598785</v>
+        <v>0.06596505641937256</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.02174537070095539</v>
+        <v>0.0008646459318697453</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.02686660178005695</v>
+        <v>0.05591155961155891</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.04716358706355095</v>
+        <v>0.007402132265269756</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.001370164100080729</v>
+        <v>0.0618990994989872</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0639498382806778</v>
+        <v>0.04266268387436867</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02284926548600197</v>
+        <v>0.04297353327274323</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.127365842461586</v>
+        <v>0.05838129669427872</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.1700231730937958</v>
+        <v>0.1182417199015617</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.1100135520100594</v>
+        <v>0.04398581013083458</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.04659232497215271</v>
+        <v>0.001781263621523976</v>
       </c>
       <c r="EG6" t="n">
-        <v>8.991919457912445e-05</v>
+        <v>0.1206144765019417</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.04237784445285797</v>
+        <v>0.003216985147446394</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.1361923664808273</v>
+        <v>0.03626716509461403</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.1197758093476295</v>
+        <v>0.02209699153900146</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.05224248766899109</v>
+        <v>0.02385727688670158</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.006557490676641464</v>
+        <v>0.0111029390245676</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.09605506062507629</v>
+        <v>0.01189320720732212</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01904300041496754</v>
+        <v>0.008425639942288399</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.03859259933233261</v>
+        <v>0.01225835643708706</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.06725014746189117</v>
+        <v>0.04911767691373825</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.009928964078426361</v>
+        <v>0.02925428189337254</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.006869291886687279</v>
+        <v>0.08796307444572449</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.05993694812059402</v>
+        <v>0.05173796787858009</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.1757265478372574</v>
+        <v>0.007206247188150883</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0008070701733231544</v>
+        <v>0.02854466810822487</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.006659485399723053</v>
+        <v>0.06341303884983063</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.03811201825737953</v>
+        <v>0.02071735449135303</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.02541914209723473</v>
+        <v>0.004367727786302567</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.01370387431234121</v>
+        <v>0.07770944386720657</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.005274359136819839</v>
+        <v>0.01424049958586693</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.04265093058347702</v>
+        <v>0.08357188850641251</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.04608007520437241</v>
+        <v>0.003745649009943008</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.04131782799959183</v>
+        <v>0.0297793373465538</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.02677316218614578</v>
+        <v>0.003056999295949936</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.002673357725143433</v>
+        <v>0.01683118380606174</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.01346011180430651</v>
+        <v>0.009110363200306892</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0298811998218298</v>
+        <v>0.005984022282063961</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.1376726627349854</v>
+        <v>0.03778783231973648</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.09248591214418411</v>
+        <v>0.01590358279645443</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02847671508789062</v>
+        <v>0.05967462062835693</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.09522442519664764</v>
+        <v>0.06904688477516174</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.07303882390260696</v>
+        <v>0.02134937793016434</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.09608428925275803</v>
+        <v>0.008050089702010155</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.04025577008724213</v>
+        <v>0.06808242946863174</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.06919564306735992</v>
+        <v>0.07104562222957611</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.08539390563964844</v>
+        <v>0.000909510999917984</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.08150556683540344</v>
+        <v>0.02322686463594437</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.06141851842403412</v>
+        <v>0.0643007755279541</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.1280750036239624</v>
+        <v>0.09590878337621689</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2918100655078888</v>
+        <v>0.1294811069965363</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.07280909270048141</v>
+        <v>0.1024322509765625</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2070415914058685</v>
+        <v>0.02242710068821907</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.01729526370763779</v>
+        <v>0.02081541158258915</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.007848531939089298</v>
+        <v>0.01179584860801697</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.02026910707354546</v>
+        <v>0.005890245549380779</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.05148264765739441</v>
+        <v>0.04441861063241959</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01654068008065224</v>
+        <v>0.02851114794611931</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.001112494617700577</v>
+        <v>0.0001142248511314392</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1337976455688477</v>
+        <v>0.1088003367185593</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.02161900699138641</v>
+        <v>0.01442501693964005</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.1691654026508331</v>
+        <v>0.04678656160831451</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.02602415531873703</v>
+        <v>0.05890663713216782</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.03305090963840485</v>
+        <v>0.022994264960289</v>
       </c>
     </row>
   </sheetData>
